--- a/data/trans_camb/P19C04-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C04-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 17,85</t>
+          <t>0,93; 17,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 7,68</t>
+          <t>-8,4; 7,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,88; -0,07</t>
+          <t>-13,72; 0,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 11,99</t>
+          <t>-2,66; 11,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 5,08</t>
+          <t>-8,47; 4,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 0,18</t>
+          <t>-11,39; 0,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 12,45</t>
+          <t>2,05; 13,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 5,08</t>
+          <t>-5,87; 5,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,93; -1,38</t>
+          <t>-10,59; -1,28</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 111,36</t>
+          <t>2,37; 110,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 49,05</t>
+          <t>-32,91; 46,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 0,65</t>
+          <t>-54,63; 1,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 101,63</t>
+          <t>-14,86; 103,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,76; 44,52</t>
+          <t>-44,63; 41,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,43; 3,89</t>
+          <t>-55,75; 7,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,2; 85,19</t>
+          <t>8,5; 87,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 35,27</t>
+          <t>-29,05; 32,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,77; -8,88</t>
+          <t>-51,75; -8,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 11,29</t>
+          <t>-2,09; 10,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 0,99</t>
+          <t>-11,31; 0,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,16; -10,25</t>
+          <t>-21,57; -10,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,89</t>
+          <t>-7,1; 3,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -1,82</t>
+          <t>-11,6; -1,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -7,49</t>
+          <t>-15,56; -7,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 5,27</t>
+          <t>-3,2; 5,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -2,3</t>
+          <t>-9,97; -2,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,13; -10,16</t>
+          <t>-16,94; -10,29</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 54,47</t>
+          <t>-8,26; 50,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 4,66</t>
+          <t>-42,35; 3,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,37; -46,62</t>
+          <t>-79,72; -47,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,72; 15,66</t>
+          <t>-31,58; 18,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,64; -9,9</t>
+          <t>-52,59; -6,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,12; -43,74</t>
+          <t>-69,33; -42,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 27,68</t>
+          <t>-13,45; 28,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,69; -11,3</t>
+          <t>-42,32; -11,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,08; -51,85</t>
+          <t>-71,74; -51,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 13,99</t>
+          <t>-0,86; 14,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,82; -3,78</t>
+          <t>-16,97; -3,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 3,83</t>
+          <t>-9,87; 2,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 13,16</t>
+          <t>2,1; 14,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 0,96</t>
+          <t>-9,44; 1,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 8,17</t>
+          <t>-2,18; 7,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 12,22</t>
+          <t>2,32; 11,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -2,88</t>
+          <t>-10,84; -2,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 4,23</t>
+          <t>-3,2; 4,61</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 80,0</t>
+          <t>-4,32; 80,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,64; -21,85</t>
+          <t>-66,15; -19,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 24,18</t>
+          <t>-38,88; 16,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 132,78</t>
+          <t>12,35; 148,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,23; 11,09</t>
+          <t>-59,45; 11,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 93,5</t>
+          <t>-13,69; 84,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,17; 87,93</t>
+          <t>10,92; 87,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,5; -20,21</t>
+          <t>-57,32; -20,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 29,84</t>
+          <t>-17,61; 33,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 19,17</t>
+          <t>6,32; 18,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 13,37</t>
+          <t>0,84; 13,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 6,71</t>
+          <t>-6,29; 6,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 12,06</t>
+          <t>1,22; 12,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 7,16</t>
+          <t>-3,5; 7,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 1,21</t>
+          <t>-8,46; 0,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 13,85</t>
+          <t>5,21; 13,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,72</t>
+          <t>0,46; 8,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1,59</t>
+          <t>-6,77; 1,54</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31,58; 152,48</t>
+          <t>31,59; 144,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 107,07</t>
+          <t>4,02; 101,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 49,19</t>
+          <t>-32,71; 50,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,96; 130,35</t>
+          <t>8,24; 137,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 79,91</t>
+          <t>-25,8; 78,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,29; 12,83</t>
+          <t>-60,2; 9,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,18; 118,92</t>
+          <t>33,51; 121,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 74,6</t>
+          <t>2,87; 75,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 13,29</t>
+          <t>-42,94; 14,05</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 16,74</t>
+          <t>-1,9; 17,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 4,89</t>
+          <t>-13,37; 4,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 7,9</t>
+          <t>-8,15; 7,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 15,26</t>
+          <t>-1,87; 15,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 9,19</t>
+          <t>-7,07; 9,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 3,86</t>
+          <t>-8,34; 3,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 13,69</t>
+          <t>0,45; 13,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 4,31</t>
+          <t>-8,81; 4,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 3,17</t>
+          <t>-6,6; 3,46</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 101,09</t>
+          <t>-7,95; 107,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,72; 29,93</t>
+          <t>-52,56; 27,11</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 50,37</t>
+          <t>-31,02; 46,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 145,39</t>
+          <t>-11,89; 134,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 82,45</t>
+          <t>-39,18; 89,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 38,72</t>
+          <t>-43,68; 38,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,45; 89,16</t>
+          <t>1,48; 87,95</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-37,32; 26,89</t>
+          <t>-41,74; 26,57</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 21,13</t>
+          <t>-31,88; 23,09</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>7,86; 24,79</t>
+          <t>8,47; 25,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,13; 20,57</t>
+          <t>4,41; 20,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 10,28</t>
+          <t>-3,18; 10,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,64; 19,88</t>
+          <t>5,74; 19,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,13; 16,34</t>
+          <t>2,88; 17,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,89; 15,04</t>
+          <t>4,02; 14,9</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,39; 19,97</t>
+          <t>10,07; 20,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>6,1; 16,09</t>
+          <t>6,02; 16,29</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,8; 11,3</t>
+          <t>2,67; 10,97</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>37,79; 214,41</t>
+          <t>39,04; 213,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24,94; 172,49</t>
+          <t>22,05; 173,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 88,28</t>
+          <t>-15,42; 86,22</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>47,59; 279,85</t>
+          <t>35,59; 277,69</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18,72; 215,31</t>
+          <t>18,9; 247,78</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,82; 220,37</t>
+          <t>24,39; 208,9</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,4; 187,91</t>
+          <t>59,25; 195,3</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>41,41; 158,57</t>
+          <t>39,06; 162,82</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17,54; 112,88</t>
+          <t>17,09; 103,64</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 5,91</t>
+          <t>-4,37; 6,14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -0,51</t>
+          <t>-11,2; -1,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,46; -2,63</t>
+          <t>-12,0; -2,66</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 2,11</t>
+          <t>-6,57; 2,36</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,87</t>
+          <t>-8,96; -0,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -4,14</t>
+          <t>-14,08; -4,27</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,28</t>
+          <t>-3,98; 2,63</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,79; -2,31</t>
+          <t>-8,64; -2,16</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -5,19</t>
+          <t>-12,65; -4,86</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 34,77</t>
+          <t>-19,86; 36,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,95; -0,44</t>
+          <t>-50,33; -7,96</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,52; -13,14</t>
+          <t>-54,25; -15,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 16,13</t>
+          <t>-38,42; 17,27</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-51,69; -5,0</t>
+          <t>-52,51; -1,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,58; -29,89</t>
+          <t>-78,65; -31,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 14,98</t>
+          <t>-20,75; 17,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-45,77; -13,83</t>
+          <t>-45,68; -13,39</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-67,09; -32,26</t>
+          <t>-66,93; -31,08</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 2,0</t>
+          <t>-7,89; 1,69</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 1,04</t>
+          <t>-7,78; 1,15</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 3,54</t>
+          <t>-14,23; 3,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,97</t>
+          <t>-3,07; 4,96</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 2,96</t>
+          <t>-4,85; 3,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 0,41</t>
+          <t>-6,58; 0,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,86</t>
+          <t>-4,27; 1,89</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,94</t>
+          <t>-5,38; 0,58</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 0,5</t>
+          <t>-9,58; 0,58</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-33,4; 12,44</t>
+          <t>-34,69; 10,36</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-34,87; 5,8</t>
+          <t>-35,18; 6,73</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 18,54</t>
+          <t>-66,07; 16,88</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 37,45</t>
+          <t>-19,2; 39,7</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 26,57</t>
+          <t>-29,82; 24,81</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 3,56</t>
+          <t>-39,1; 5,85</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 11,82</t>
+          <t>-22,81; 12,18</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 7,34</t>
+          <t>-28,8; 3,97</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-55,01; 2,86</t>
+          <t>-50,44; 3,2</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,2</t>
+          <t>2,52; 7,13</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,14</t>
+          <t>-4,17; 0,13</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -3,18</t>
+          <t>-8,61; -3,2</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,68</t>
+          <t>0,98; 4,74</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,16</t>
+          <t>-3,55; 0,22</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,6; -2,49</t>
+          <t>-6,57; -2,5</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,38</t>
+          <t>2,21; 5,3</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,37</t>
+          <t>-3,19; -0,34</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,54; -3,18</t>
+          <t>-6,47; -3,15</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>12,62; 38,29</t>
+          <t>12,37; 37,62</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 0,77</t>
+          <t>-20,25; 0,53</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-43,77; -16,69</t>
+          <t>-43,49; -17,26</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6,15; 34,4</t>
+          <t>6,27; 35,02</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 1,08</t>
+          <t>-23,02; 1,65</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-42,44; -18,24</t>
+          <t>-42,41; -18,18</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12,99; 32,41</t>
+          <t>12,21; 32,94</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-18,37; -2,27</t>
+          <t>-17,79; -2,1</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-37,57; -19,33</t>
+          <t>-36,86; -19,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C04-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C04-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,04</t>
+          <t>-5,03</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,98</t>
+          <t>-5,01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,9</t>
+          <t>-4,99</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 17,67</t>
+          <t>0,69; 17,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 7,5</t>
+          <t>-8,01; 7,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 0,23</t>
+          <t>-13,35; 1,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 11,62</t>
+          <t>-3,41; 11,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 4,77</t>
+          <t>-8,91; 4,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 0,5</t>
+          <t>-10,49; 0,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,27</t>
+          <t>1,47; 12,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 5,05</t>
+          <t>-5,48; 4,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,59; -1,28</t>
+          <t>-9,31; -0,27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-34,52%</t>
+          <t>-24,66%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-32,22%</t>
+          <t>-32,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-33,06%</t>
+          <t>-27,94%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 110,72</t>
+          <t>1,36; 107,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 46,77</t>
+          <t>-32,28; 46,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 1,85</t>
+          <t>-49,98; 10,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 103,63</t>
+          <t>-19,0; 92,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 41,52</t>
+          <t>-44,26; 40,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 7,73</t>
+          <t>-53,95; 8,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 87,83</t>
+          <t>8,04; 88,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 32,77</t>
+          <t>-27,21; 34,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,75; -8,57</t>
+          <t>-45,31; -3,08</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-16,02</t>
+          <t>-16,09</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,32</t>
+          <t>-11,58</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-13,6</t>
+          <t>-13,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 10,63</t>
+          <t>-2,09; 10,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 0,73</t>
+          <t>-11,62; 0,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -10,55</t>
+          <t>-20,83; -10,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 3,2</t>
+          <t>-7,05; 3,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,6; -1,2</t>
+          <t>-11,92; -1,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -7,17</t>
+          <t>-15,73; -7,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,42</t>
+          <t>-2,71; 5,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,97; -2,2</t>
+          <t>-9,84; -2,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -10,29</t>
+          <t>-17,22; -10,48</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-67,62%</t>
+          <t>-67,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-58,07%</t>
+          <t>-59,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-63,19%</t>
+          <t>-63,93%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 50,64</t>
+          <t>-8,52; 51,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,35; 3,77</t>
+          <t>-42,77; 1,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,72; -47,21</t>
+          <t>-79,84; -51,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,58; 18,19</t>
+          <t>-31,19; 19,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,59; -6,51</t>
+          <t>-53,9; -10,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,33; -42,74</t>
+          <t>-70,61; -44,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 28,05</t>
+          <t>-11,53; 27,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,32; -11,09</t>
+          <t>-42,47; -11,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,74; -51,94</t>
+          <t>-72,21; -53,62</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,06</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>3,61</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>1,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 14,29</t>
+          <t>-1,56; 13,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -3,6</t>
+          <t>-16,58; -4,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 2,7</t>
+          <t>-8,65; 4,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 14,43</t>
+          <t>1,46; 13,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 1,07</t>
+          <t>-8,86; 0,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 7,77</t>
+          <t>-0,91; 8,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 11,84</t>
+          <t>2,39; 11,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,84; -2,87</t>
+          <t>-11,03; -2,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 4,61</t>
+          <t>-2,74; 5,44</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-14,37%</t>
+          <t>-8,48%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 80,65</t>
+          <t>-6,62; 73,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,15; -19,91</t>
+          <t>-64,95; -23,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 16,08</t>
+          <t>-34,22; 30,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,35; 148,29</t>
+          <t>9,15; 148,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,45; 11,55</t>
+          <t>-59,0; 6,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 84,02</t>
+          <t>-6,23; 88,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,92; 87,58</t>
+          <t>12,19; 85,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,32; -20,28</t>
+          <t>-57,62; -20,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 33,88</t>
+          <t>-14,32; 39,96</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,55</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-0,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 18,64</t>
+          <t>5,66; 19,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 13,18</t>
+          <t>0,96; 13,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 6,56</t>
+          <t>-5,27; 8,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 12,06</t>
+          <t>0,64; 12,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 7,11</t>
+          <t>-3,42; 7,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 0,99</t>
+          <t>-6,16; 3,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 13,69</t>
+          <t>5,33; 14,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 8,52</t>
+          <t>0,47; 8,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 1,54</t>
+          <t>-3,76; 3,8</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-30,8%</t>
+          <t>-10,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-17,61%</t>
+          <t>-0,31%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31,59; 144,99</t>
+          <t>27,23; 146,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,02; 101,5</t>
+          <t>2,59; 106,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 50,41</t>
+          <t>-28,51; 60,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,24; 137,13</t>
+          <t>4,38; 134,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 78,7</t>
+          <t>-24,31; 86,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,2; 9,9</t>
+          <t>-40,57; 39,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,51; 121,53</t>
+          <t>33,65; 120,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 75,86</t>
+          <t>3,5; 77,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 14,05</t>
+          <t>-23,66; 33,37</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-0,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 17,08</t>
+          <t>-1,45; 17,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 4,89</t>
+          <t>-13,6; 3,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 7,42</t>
+          <t>-6,88; 8,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 15,36</t>
+          <t>-1,5; 15,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 9,5</t>
+          <t>-7,81; 9,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 3,99</t>
+          <t>-8,01; 5,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 13,26</t>
+          <t>0,24; 13,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 4,12</t>
+          <t>-8,35; 4,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 3,46</t>
+          <t>-5,35; 4,83</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-1,61%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-13,49%</t>
+          <t>-9,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-8,36%</t>
+          <t>-2,78%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 107,68</t>
+          <t>-6,37; 96,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-52,56; 27,11</t>
+          <t>-52,92; 22,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 46,57</t>
+          <t>-26,12; 53,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 134,81</t>
+          <t>-8,41; 145,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,18; 89,07</t>
+          <t>-40,55; 85,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 38,1</t>
+          <t>-40,69; 50,07</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,48; 87,95</t>
+          <t>0,59; 88,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 26,57</t>
+          <t>-39,24; 29,34</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 23,09</t>
+          <t>-24,93; 33,89</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>7,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>8,47; 25,09</t>
+          <t>8,86; 25,32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,41; 20,43</t>
+          <t>4,8; 20,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 10,1</t>
+          <t>-2,37; 11,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,74; 19,77</t>
+          <t>6,35; 19,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,88; 17,12</t>
+          <t>3,42; 17,15</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,02; 14,9</t>
+          <t>4,64; 15,47</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,07; 20,36</t>
+          <t>9,89; 20,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>6,02; 16,29</t>
+          <t>6,02; 16,5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,67; 10,97</t>
+          <t>2,72; 11,67</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39,04; 213,56</t>
+          <t>42,54; 206,15</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>22,05; 173,02</t>
+          <t>24,53; 176,23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 86,22</t>
+          <t>-12,82; 102,51</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35,59; 277,69</t>
+          <t>46,65; 284,56</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18,9; 247,78</t>
+          <t>23,61; 246,41</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,39; 208,9</t>
+          <t>31,55; 218,6</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>59,25; 195,3</t>
+          <t>59,94; 196,37</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>39,06; 162,82</t>
+          <t>38,48; 155,57</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17,09; 103,64</t>
+          <t>16,36; 117,2</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-7,32</t>
+          <t>-7,15</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-8,16</t>
+          <t>-6,07</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-7,99</t>
+          <t>-6,5</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 6,14</t>
+          <t>-4,19; 5,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,2; -1,37</t>
+          <t>-11,37; -0,66</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,0; -2,66</t>
+          <t>-11,43; -2,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 2,36</t>
+          <t>-6,4; 1,97</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -0,21</t>
+          <t>-8,81; -0,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -4,27</t>
+          <t>-10,14; -2,9</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,63</t>
+          <t>-3,92; 2,73</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,64; -2,16</t>
+          <t>-8,48; -1,95</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-12,65; -4,86</t>
+          <t>-9,4; -3,71</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-37,41%</t>
+          <t>-36,58%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-53,46%</t>
+          <t>-39,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-46,31%</t>
+          <t>-37,68%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 36,78</t>
+          <t>-19,09; 33,32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-50,33; -7,96</t>
+          <t>-51,34; -3,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,25; -15,01</t>
+          <t>-52,37; -14,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 17,27</t>
+          <t>-35,83; 16,39</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-52,51; -1,42</t>
+          <t>-51,95; -5,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,65; -31,33</t>
+          <t>-55,29; -21,64</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 17,94</t>
+          <t>-21,03; 16,84</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-45,68; -13,39</t>
+          <t>-44,78; -12,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,93; -31,08</t>
+          <t>-49,81; -24,32</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-4,18</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,16</t>
+          <t>-0,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1,69</t>
+          <t>-7,81; 1,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 1,15</t>
+          <t>-8,25; 0,96</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 3,16</t>
+          <t>-2,31; 6,66</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,96</t>
+          <t>-3,23; 4,92</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 3,08</t>
+          <t>-4,85; 2,76</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 0,61</t>
+          <t>-6,31; 0,82</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,89</t>
+          <t>-4,14; 2,28</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,58</t>
+          <t>-5,34; 0,72</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 0,58</t>
+          <t>-3,02; 2,52</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-21,14%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-20,72%</t>
+          <t>-18,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-18,66%</t>
+          <t>-1,16%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 10,36</t>
+          <t>-34,97; 8,8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 6,73</t>
+          <t>-36,74; 5,32</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 16,88</t>
+          <t>-10,55; 40,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 39,7</t>
+          <t>-19,52; 41,16</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 24,81</t>
+          <t>-30,78; 23,2</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 5,85</t>
+          <t>-38,18; 6,78</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 12,18</t>
+          <t>-22,37; 15,04</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 3,97</t>
+          <t>-28,44; 4,77</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 3,2</t>
+          <t>-16,95; 16,51</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-4,17</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-3,32</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,13</t>
+          <t>2,46; 7,08</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,13</t>
+          <t>-4,02; 0,25</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,61; -3,2</t>
+          <t>-5,81; -1,6</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,74</t>
+          <t>1,04; 4,88</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,22</t>
+          <t>-3,51; 0,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,57; -2,5</t>
+          <t>-4,9; -1,67</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,3</t>
+          <t>2,27; 5,27</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,34</t>
+          <t>-3,51; -0,44</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -3,15</t>
+          <t>-4,56; -2,07</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-27,5%</t>
+          <t>-17,95%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-28,39%</t>
+          <t>-21,66%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-27,64%</t>
+          <t>-19,31%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>12,37; 37,62</t>
+          <t>11,63; 37,63</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 0,53</t>
+          <t>-19,34; 1,36</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-43,49; -17,26</t>
+          <t>-27,19; -8,33</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6,27; 35,02</t>
+          <t>6,6; 35,07</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 1,65</t>
+          <t>-22,41; 1,9</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -18,18</t>
+          <t>-30,54; -12,32</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12,21; 32,94</t>
+          <t>12,47; 31,82</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -2,1</t>
+          <t>-19,17; -2,6</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-36,86; -19,06</t>
+          <t>-25,4; -12,53</t>
         </is>
       </c>
     </row>
